--- a/source/8、绩效异常岗位/4、供件岗/供件岗-6月.xlsx
+++ b/source/8、绩效异常岗位/4、供件岗/供件岗-6月.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="68">
   <si>
     <t>数据日期</t>
   </si>
@@ -64,15 +64,9 @@
     <t>肃宁</t>
   </si>
   <si>
-    <t>75.2</t>
-  </si>
-  <si>
     <t>石家庄</t>
   </si>
   <si>
-    <t>40.2</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -82,111 +76,72 @@
     <t>呼和浩特</t>
   </si>
   <si>
-    <t>73.1</t>
-  </si>
-  <si>
     <t>山西区</t>
   </si>
   <si>
     <t>太原</t>
   </si>
   <si>
-    <t>94</t>
-  </si>
-  <si>
     <t>宁夏区</t>
   </si>
   <si>
     <t>银川</t>
   </si>
   <si>
-    <t>53.8</t>
-  </si>
-  <si>
     <t>湖南区</t>
   </si>
   <si>
     <t>衡阳</t>
   </si>
   <si>
-    <t>72.4</t>
-  </si>
-  <si>
     <t>广西区</t>
   </si>
   <si>
     <t>柳州</t>
   </si>
   <si>
-    <t>55.5</t>
-  </si>
-  <si>
     <t>天津区</t>
   </si>
   <si>
     <t>天津</t>
   </si>
   <si>
-    <t>81.7</t>
-  </si>
-  <si>
     <t>长沙</t>
   </si>
   <si>
-    <t>95.7</t>
-  </si>
-  <si>
     <t>邢邯</t>
   </si>
   <si>
-    <t>57.9</t>
-  </si>
-  <si>
     <t>贵州区</t>
   </si>
   <si>
     <t>贵阳</t>
   </si>
   <si>
-    <t>106.4</t>
-  </si>
-  <si>
     <t>湖北区</t>
   </si>
   <si>
     <t>武汉</t>
   </si>
   <si>
-    <t>83.2</t>
-  </si>
-  <si>
     <t>辽宁区</t>
   </si>
   <si>
     <t>沈阳</t>
   </si>
   <si>
-    <t>75</t>
-  </si>
-  <si>
     <t>河南区</t>
   </si>
   <si>
     <t>商丘</t>
   </si>
   <si>
-    <t>61.5</t>
-  </si>
-  <si>
     <t>黑龙江区</t>
   </si>
   <si>
     <t>哈尔滨</t>
   </si>
   <si>
-    <t>79.1</t>
-  </si>
-  <si>
     <t>山东区</t>
   </si>
   <si>
@@ -196,76 +151,88 @@
     <t>盘锦</t>
   </si>
   <si>
-    <t>71.8</t>
-  </si>
-  <si>
     <t>吉林区</t>
   </si>
   <si>
     <t>长春</t>
   </si>
   <si>
-    <t>76.8</t>
-  </si>
-  <si>
     <t>青岛</t>
   </si>
   <si>
-    <t>76.9</t>
-  </si>
-  <si>
     <t>江苏区</t>
   </si>
   <si>
     <t>南通</t>
   </si>
   <si>
-    <t>108.7</t>
-  </si>
-  <si>
     <t>浙南区</t>
   </si>
   <si>
     <t>义乌</t>
   </si>
   <si>
-    <t>147.8</t>
-  </si>
-  <si>
     <t>广东区</t>
   </si>
   <si>
     <t>深圳</t>
   </si>
   <si>
-    <t>97.5</t>
-  </si>
-  <si>
     <t>安徽区</t>
   </si>
   <si>
     <t>芜湖</t>
   </si>
   <si>
-    <t>97.4</t>
-  </si>
-  <si>
     <t>合肥</t>
   </si>
   <si>
-    <t>108.6</t>
-  </si>
-  <si>
     <t>佛山</t>
   </si>
   <si>
-    <t>107.6</t>
-  </si>
-  <si>
     <t>广州</t>
   </si>
   <si>
-    <t>112.5</t>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>福建区</t>
+  </si>
+  <si>
+    <t>泉州</t>
+  </si>
+  <si>
+    <t>云南区</t>
+  </si>
+  <si>
+    <t>昆明</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>浙北区</t>
+  </si>
+  <si>
+    <t>东方天地港</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>甘肃区</t>
+  </si>
+  <si>
+    <t>兰州</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>四川区</t>
+  </si>
+  <si>
+    <t>成都</t>
   </si>
 </sst>
 </file>
@@ -1196,7 +1163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1235,8 +1202,8 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
+      <c r="D2">
+        <v>75.2</v>
       </c>
       <c r="E2">
         <v>111.8</v>
@@ -1259,10 +1226,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>40.2</v>
       </c>
       <c r="E3">
         <v>55</v>
@@ -1271,10 +1238,10 @@
         <v>36.9</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1282,13 +1249,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>73.1</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -1308,13 +1275,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>94</v>
       </c>
       <c r="E5">
         <v>118.7</v>
@@ -1334,13 +1301,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>53.8</v>
       </c>
       <c r="E6">
         <v>67.3</v>
@@ -1349,10 +1316,10 @@
         <v>25.1</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1360,13 +1327,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>72.4</v>
       </c>
       <c r="E7">
         <v>90.5</v>
@@ -1375,10 +1342,10 @@
         <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1386,13 +1353,13 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>55.5</v>
       </c>
       <c r="E8">
         <v>68.3</v>
@@ -1401,10 +1368,10 @@
         <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1412,13 +1379,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>81.7</v>
       </c>
       <c r="E9">
         <v>99.1</v>
@@ -1438,13 +1405,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="D10">
+        <v>95.7</v>
       </c>
       <c r="E10">
         <v>115.3</v>
@@ -1467,10 +1434,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" t="s">
-        <v>36</v>
+        <v>26</v>
+      </c>
+      <c r="D11">
+        <v>57.9</v>
       </c>
       <c r="E11">
         <v>69.7</v>
@@ -1479,10 +1446,10 @@
         <v>20.3</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1490,13 +1457,13 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>39</v>
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <v>106.4</v>
       </c>
       <c r="E12">
         <v>127.7</v>
@@ -1516,13 +1483,13 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
+        <v>30</v>
+      </c>
+      <c r="D13">
+        <v>83.2</v>
       </c>
       <c r="E13">
         <v>99.4</v>
@@ -1542,13 +1509,13 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>45</v>
+        <v>32</v>
+      </c>
+      <c r="D14">
+        <v>75</v>
       </c>
       <c r="E14">
         <v>89.5</v>
@@ -1557,10 +1524,10 @@
         <v>19.2</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1568,13 +1535,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" t="s">
-        <v>48</v>
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>61.5</v>
       </c>
       <c r="E15">
         <v>72.4</v>
@@ -1583,10 +1550,10 @@
         <v>17.7</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1594,13 +1561,13 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>51</v>
+        <v>36</v>
+      </c>
+      <c r="D16">
+        <v>79.1</v>
       </c>
       <c r="E16">
         <v>92</v>
@@ -1609,10 +1576,10 @@
         <v>16.3</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1620,13 +1587,13 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>11</v>
+        <v>38</v>
+      </c>
+      <c r="D17">
+        <v>75.2</v>
       </c>
       <c r="E17">
         <v>86.8</v>
@@ -1635,10 +1602,10 @@
         <v>15.3</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1646,13 +1613,13 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" t="s">
-        <v>55</v>
+        <v>39</v>
+      </c>
+      <c r="D18">
+        <v>71.8</v>
       </c>
       <c r="E18">
         <v>82</v>
@@ -1661,10 +1628,10 @@
         <v>14.1</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1672,13 +1639,13 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" t="s">
-        <v>58</v>
+        <v>41</v>
+      </c>
+      <c r="D19">
+        <v>76.8</v>
       </c>
       <c r="E19">
         <v>87.6</v>
@@ -1687,10 +1654,10 @@
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1698,13 +1665,13 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" t="s">
-        <v>60</v>
+        <v>42</v>
+      </c>
+      <c r="D20">
+        <v>76.9</v>
       </c>
       <c r="E20">
         <v>85.2</v>
@@ -1713,10 +1680,10 @@
         <v>10.8</v>
       </c>
       <c r="G20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1724,13 +1691,13 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" t="s">
-        <v>63</v>
+        <v>44</v>
+      </c>
+      <c r="D21">
+        <v>108.7</v>
       </c>
       <c r="E21">
         <v>118.7</v>
@@ -1750,13 +1717,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" t="s">
-        <v>66</v>
+        <v>46</v>
+      </c>
+      <c r="D22">
+        <v>147.8</v>
       </c>
       <c r="E22">
         <v>160.7</v>
@@ -1776,13 +1743,13 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" t="s">
-        <v>69</v>
+        <v>48</v>
+      </c>
+      <c r="D23">
+        <v>97.5</v>
       </c>
       <c r="E23">
         <v>104.9</v>
@@ -1802,13 +1769,13 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" t="s">
-        <v>72</v>
+        <v>50</v>
+      </c>
+      <c r="D24">
+        <v>97.4</v>
       </c>
       <c r="E24">
         <v>103.5</v>
@@ -1828,13 +1795,13 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" t="s">
-        <v>74</v>
+        <v>51</v>
+      </c>
+      <c r="D25">
+        <v>108.6</v>
       </c>
       <c r="E25">
         <v>109.5</v>
@@ -1854,13 +1821,13 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" t="s">
-        <v>76</v>
+        <v>52</v>
+      </c>
+      <c r="D26">
+        <v>107.6</v>
       </c>
       <c r="E26">
         <v>106.5</v>
@@ -1880,13 +1847,13 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" t="s">
-        <v>78</v>
+        <v>53</v>
+      </c>
+      <c r="D27">
+        <v>112.5</v>
       </c>
       <c r="E27">
         <v>109.2</v>
@@ -1899,6 +1866,2372 @@
       </c>
       <c r="H27">
         <v>18.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>40.2</v>
+      </c>
+      <c r="E28">
+        <v>51.6</v>
+      </c>
+      <c r="F28">
+        <v>28.4</v>
+      </c>
+      <c r="G28" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29">
+        <v>75.2</v>
+      </c>
+      <c r="E29">
+        <v>94.9</v>
+      </c>
+      <c r="F29">
+        <v>26.1</v>
+      </c>
+      <c r="G29">
+        <v>90.7</v>
+      </c>
+      <c r="H29">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30">
+        <v>73.1</v>
+      </c>
+      <c r="E30">
+        <v>90.1</v>
+      </c>
+      <c r="F30">
+        <v>23.2</v>
+      </c>
+      <c r="G30" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31">
+        <v>57.9</v>
+      </c>
+      <c r="E31">
+        <v>71.3</v>
+      </c>
+      <c r="F31">
+        <v>23.2</v>
+      </c>
+      <c r="G31" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32">
+        <v>75.2</v>
+      </c>
+      <c r="E32">
+        <v>89.6</v>
+      </c>
+      <c r="F32">
+        <v>19.1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33">
+        <v>53.8</v>
+      </c>
+      <c r="E33">
+        <v>62.6</v>
+      </c>
+      <c r="F33">
+        <v>16.3</v>
+      </c>
+      <c r="G33" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34">
+        <v>61.5</v>
+      </c>
+      <c r="E34">
+        <v>71.3</v>
+      </c>
+      <c r="F34">
+        <v>15.8</v>
+      </c>
+      <c r="G34" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35">
+        <v>79.1</v>
+      </c>
+      <c r="E35">
+        <v>90.5</v>
+      </c>
+      <c r="F35">
+        <v>14.4</v>
+      </c>
+      <c r="G35" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36">
+        <v>76.6</v>
+      </c>
+      <c r="E36">
+        <v>87.2</v>
+      </c>
+      <c r="F36">
+        <v>13.7</v>
+      </c>
+      <c r="G36" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37">
+        <v>98.7</v>
+      </c>
+      <c r="E37">
+        <v>111.1</v>
+      </c>
+      <c r="F37">
+        <v>12.5</v>
+      </c>
+      <c r="G37">
+        <v>90.7</v>
+      </c>
+      <c r="H37">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38">
+        <v>72.4</v>
+      </c>
+      <c r="E38">
+        <v>80.5</v>
+      </c>
+      <c r="F38">
+        <v>11.1</v>
+      </c>
+      <c r="G38" t="s">
+        <v>12</v>
+      </c>
+      <c r="H38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39">
+        <v>96.3</v>
+      </c>
+      <c r="E39">
+        <v>107</v>
+      </c>
+      <c r="F39">
+        <v>11</v>
+      </c>
+      <c r="G39">
+        <v>90.7</v>
+      </c>
+      <c r="H39">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40">
+        <v>106.4</v>
+      </c>
+      <c r="E40">
+        <v>118</v>
+      </c>
+      <c r="F40">
+        <v>10.9</v>
+      </c>
+      <c r="G40">
+        <v>90.7</v>
+      </c>
+      <c r="H40">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41">
+        <v>76.9</v>
+      </c>
+      <c r="E41">
+        <v>84.9</v>
+      </c>
+      <c r="F41">
+        <v>10.4</v>
+      </c>
+      <c r="G41" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42">
+        <v>148.8</v>
+      </c>
+      <c r="E42">
+        <v>164</v>
+      </c>
+      <c r="F42">
+        <v>10.2</v>
+      </c>
+      <c r="G42">
+        <v>90.7</v>
+      </c>
+      <c r="H42">
+        <v>80.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43">
+        <v>97.5</v>
+      </c>
+      <c r="E43">
+        <v>105.9</v>
+      </c>
+      <c r="F43">
+        <v>8.6</v>
+      </c>
+      <c r="G43">
+        <v>90.7</v>
+      </c>
+      <c r="H43">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" t="s">
+        <v>50</v>
+      </c>
+      <c r="D44">
+        <v>97.4</v>
+      </c>
+      <c r="E44">
+        <v>103.9</v>
+      </c>
+      <c r="F44">
+        <v>6.6</v>
+      </c>
+      <c r="G44">
+        <v>90.7</v>
+      </c>
+      <c r="H44">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45">
+        <v>108.2</v>
+      </c>
+      <c r="E45">
+        <v>114.3</v>
+      </c>
+      <c r="F45">
+        <v>5.6</v>
+      </c>
+      <c r="G45">
+        <v>90.7</v>
+      </c>
+      <c r="H45">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46">
+        <v>98.3</v>
+      </c>
+      <c r="E46">
+        <v>103.3</v>
+      </c>
+      <c r="F46">
+        <v>5.1</v>
+      </c>
+      <c r="G46">
+        <v>90.7</v>
+      </c>
+      <c r="H46">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47">
+        <v>108.7</v>
+      </c>
+      <c r="E47">
+        <v>112.7</v>
+      </c>
+      <c r="F47">
+        <v>3.6</v>
+      </c>
+      <c r="G47">
+        <v>90.7</v>
+      </c>
+      <c r="H47">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" t="s">
+        <v>52</v>
+      </c>
+      <c r="D48">
+        <v>107.6</v>
+      </c>
+      <c r="E48">
+        <v>107.6</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>90.7</v>
+      </c>
+      <c r="H48">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49">
+        <v>112.5</v>
+      </c>
+      <c r="E49">
+        <v>110.9</v>
+      </c>
+      <c r="F49">
+        <v>-1.4</v>
+      </c>
+      <c r="G49">
+        <v>90.7</v>
+      </c>
+      <c r="H49">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" t="s">
+        <v>58</v>
+      </c>
+      <c r="D50">
+        <v>108.6</v>
+      </c>
+      <c r="E50">
+        <v>102.9</v>
+      </c>
+      <c r="F50">
+        <v>-5.2</v>
+      </c>
+      <c r="G50">
+        <v>90.7</v>
+      </c>
+      <c r="H50">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51">
+        <v>40.2</v>
+      </c>
+      <c r="E51">
+        <v>51.1</v>
+      </c>
+      <c r="F51">
+        <v>27.2</v>
+      </c>
+      <c r="G51" t="s">
+        <v>12</v>
+      </c>
+      <c r="H51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52">
+        <v>75.2</v>
+      </c>
+      <c r="E52">
+        <v>91.1</v>
+      </c>
+      <c r="F52">
+        <v>21.1</v>
+      </c>
+      <c r="G52">
+        <v>90.5</v>
+      </c>
+      <c r="H52">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53">
+        <v>73.1</v>
+      </c>
+      <c r="E53">
+        <v>87.1</v>
+      </c>
+      <c r="F53">
+        <v>19.1</v>
+      </c>
+      <c r="G53" t="s">
+        <v>12</v>
+      </c>
+      <c r="H53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" t="s">
+        <v>26</v>
+      </c>
+      <c r="D54">
+        <v>57.9</v>
+      </c>
+      <c r="E54">
+        <v>68.8</v>
+      </c>
+      <c r="F54">
+        <v>18.8</v>
+      </c>
+      <c r="G54" t="s">
+        <v>12</v>
+      </c>
+      <c r="H54" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" t="s">
+        <v>33</v>
+      </c>
+      <c r="C55" t="s">
+        <v>34</v>
+      </c>
+      <c r="D55">
+        <v>61.5</v>
+      </c>
+      <c r="E55">
+        <v>71.9</v>
+      </c>
+      <c r="F55">
+        <v>16.9</v>
+      </c>
+      <c r="G55" t="s">
+        <v>12</v>
+      </c>
+      <c r="H55" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56">
+        <v>79.1</v>
+      </c>
+      <c r="E56">
+        <v>91.7</v>
+      </c>
+      <c r="F56">
+        <v>15.9</v>
+      </c>
+      <c r="G56">
+        <v>90.5</v>
+      </c>
+      <c r="H56">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57" t="s">
+        <v>38</v>
+      </c>
+      <c r="D57">
+        <v>75.2</v>
+      </c>
+      <c r="E57">
+        <v>86.6</v>
+      </c>
+      <c r="F57">
+        <v>15.1</v>
+      </c>
+      <c r="G57" t="s">
+        <v>12</v>
+      </c>
+      <c r="H57" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" t="s">
+        <v>40</v>
+      </c>
+      <c r="C58" t="s">
+        <v>41</v>
+      </c>
+      <c r="D58">
+        <v>76.6</v>
+      </c>
+      <c r="E58">
+        <v>88.3</v>
+      </c>
+      <c r="F58">
+        <v>15.1</v>
+      </c>
+      <c r="G58" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" t="s">
+        <v>25</v>
+      </c>
+      <c r="D59">
+        <v>98.7</v>
+      </c>
+      <c r="E59">
+        <v>112.3</v>
+      </c>
+      <c r="F59">
+        <v>13.7</v>
+      </c>
+      <c r="G59">
+        <v>90.5</v>
+      </c>
+      <c r="H59">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C60" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60">
+        <v>148.8</v>
+      </c>
+      <c r="E60">
+        <v>168.9</v>
+      </c>
+      <c r="F60">
+        <v>13.5</v>
+      </c>
+      <c r="G60">
+        <v>90.5</v>
+      </c>
+      <c r="H60">
+        <v>86.6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61">
+        <v>53.8</v>
+      </c>
+      <c r="E61">
+        <v>60.7</v>
+      </c>
+      <c r="F61">
+        <v>12.8</v>
+      </c>
+      <c r="G61" t="s">
+        <v>12</v>
+      </c>
+      <c r="H61" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>59</v>
+      </c>
+      <c r="B62" t="s">
+        <v>47</v>
+      </c>
+      <c r="C62" t="s">
+        <v>48</v>
+      </c>
+      <c r="D62">
+        <v>97.5</v>
+      </c>
+      <c r="E62">
+        <v>107.9</v>
+      </c>
+      <c r="F62">
+        <v>10.6</v>
+      </c>
+      <c r="G62">
+        <v>90.5</v>
+      </c>
+      <c r="H62">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>59</v>
+      </c>
+      <c r="B63" t="s">
+        <v>49</v>
+      </c>
+      <c r="C63" t="s">
+        <v>51</v>
+      </c>
+      <c r="D63">
+        <v>108.2</v>
+      </c>
+      <c r="E63">
+        <v>116.9</v>
+      </c>
+      <c r="F63">
+        <v>8</v>
+      </c>
+      <c r="G63">
+        <v>90.5</v>
+      </c>
+      <c r="H63">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>59</v>
+      </c>
+      <c r="B64" t="s">
+        <v>49</v>
+      </c>
+      <c r="C64" t="s">
+        <v>50</v>
+      </c>
+      <c r="D64">
+        <v>97.4</v>
+      </c>
+      <c r="E64">
+        <v>104.8</v>
+      </c>
+      <c r="F64">
+        <v>7.6</v>
+      </c>
+      <c r="G64">
+        <v>90.5</v>
+      </c>
+      <c r="H64">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>59</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65">
+        <v>96.3</v>
+      </c>
+      <c r="E65">
+        <v>103.1</v>
+      </c>
+      <c r="F65">
+        <v>7</v>
+      </c>
+      <c r="G65">
+        <v>90.5</v>
+      </c>
+      <c r="H65">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" t="s">
+        <v>60</v>
+      </c>
+      <c r="C66" t="s">
+        <v>61</v>
+      </c>
+      <c r="D66">
+        <v>94</v>
+      </c>
+      <c r="E66">
+        <v>100.5</v>
+      </c>
+      <c r="F66">
+        <v>6.9</v>
+      </c>
+      <c r="G66">
+        <v>90.5</v>
+      </c>
+      <c r="H66">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>59</v>
+      </c>
+      <c r="B67" t="s">
+        <v>55</v>
+      </c>
+      <c r="C67" t="s">
+        <v>56</v>
+      </c>
+      <c r="D67">
+        <v>98.3</v>
+      </c>
+      <c r="E67">
+        <v>104.8</v>
+      </c>
+      <c r="F67">
+        <v>6.6</v>
+      </c>
+      <c r="G67">
+        <v>90.5</v>
+      </c>
+      <c r="H67">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>59</v>
+      </c>
+      <c r="B68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68">
+        <v>106.4</v>
+      </c>
+      <c r="E68">
+        <v>112.9</v>
+      </c>
+      <c r="F68">
+        <v>6.1</v>
+      </c>
+      <c r="G68">
+        <v>90.5</v>
+      </c>
+      <c r="H68">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>59</v>
+      </c>
+      <c r="B69" t="s">
+        <v>43</v>
+      </c>
+      <c r="C69" t="s">
+        <v>44</v>
+      </c>
+      <c r="D69">
+        <v>108.7</v>
+      </c>
+      <c r="E69">
+        <v>112.3</v>
+      </c>
+      <c r="F69">
+        <v>3.2</v>
+      </c>
+      <c r="G69">
+        <v>90.5</v>
+      </c>
+      <c r="H69">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>59</v>
+      </c>
+      <c r="B70" t="s">
+        <v>47</v>
+      </c>
+      <c r="C70" t="s">
+        <v>52</v>
+      </c>
+      <c r="D70">
+        <v>107.6</v>
+      </c>
+      <c r="E70">
+        <v>108.3</v>
+      </c>
+      <c r="F70">
+        <v>0.6</v>
+      </c>
+      <c r="G70">
+        <v>90.5</v>
+      </c>
+      <c r="H70">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71" t="s">
+        <v>47</v>
+      </c>
+      <c r="C71" t="s">
+        <v>53</v>
+      </c>
+      <c r="D71">
+        <v>112.5</v>
+      </c>
+      <c r="E71">
+        <v>111.3</v>
+      </c>
+      <c r="F71">
+        <v>-1.1</v>
+      </c>
+      <c r="G71">
+        <v>90.5</v>
+      </c>
+      <c r="H71">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
+        <v>59</v>
+      </c>
+      <c r="B72" t="s">
+        <v>57</v>
+      </c>
+      <c r="C72" t="s">
+        <v>58</v>
+      </c>
+      <c r="D72">
+        <v>108.6</v>
+      </c>
+      <c r="E72">
+        <v>104.4</v>
+      </c>
+      <c r="F72">
+        <v>-3.9</v>
+      </c>
+      <c r="G72">
+        <v>90.5</v>
+      </c>
+      <c r="H72">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" t="s">
+        <v>9</v>
+      </c>
+      <c r="C73" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73">
+        <v>40.2</v>
+      </c>
+      <c r="E73">
+        <v>51.2</v>
+      </c>
+      <c r="F73">
+        <v>27.3</v>
+      </c>
+      <c r="G73" t="s">
+        <v>12</v>
+      </c>
+      <c r="H73" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74">
+        <v>75.2</v>
+      </c>
+      <c r="E74">
+        <v>91</v>
+      </c>
+      <c r="F74">
+        <v>21</v>
+      </c>
+      <c r="G74">
+        <v>90.6</v>
+      </c>
+      <c r="H74">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75" t="s">
+        <v>13</v>
+      </c>
+      <c r="C75" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75">
+        <v>73.1</v>
+      </c>
+      <c r="E75">
+        <v>86.7</v>
+      </c>
+      <c r="F75">
+        <v>18.4</v>
+      </c>
+      <c r="G75" t="s">
+        <v>12</v>
+      </c>
+      <c r="H75" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" t="s">
+        <v>40</v>
+      </c>
+      <c r="C76" t="s">
+        <v>41</v>
+      </c>
+      <c r="D76">
+        <v>76.6</v>
+      </c>
+      <c r="E76">
+        <v>89.2</v>
+      </c>
+      <c r="F76">
+        <v>16.3</v>
+      </c>
+      <c r="G76" t="s">
+        <v>12</v>
+      </c>
+      <c r="H76" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77">
+        <v>61.5</v>
+      </c>
+      <c r="E77">
+        <v>71.5</v>
+      </c>
+      <c r="F77">
+        <v>16.2</v>
+      </c>
+      <c r="G77" t="s">
+        <v>12</v>
+      </c>
+      <c r="H77" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" t="s">
+        <v>26</v>
+      </c>
+      <c r="D78">
+        <v>57.9</v>
+      </c>
+      <c r="E78">
+        <v>67</v>
+      </c>
+      <c r="F78">
+        <v>15.7</v>
+      </c>
+      <c r="G78" t="s">
+        <v>12</v>
+      </c>
+      <c r="H78" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>62</v>
+      </c>
+      <c r="B79" t="s">
+        <v>37</v>
+      </c>
+      <c r="C79" t="s">
+        <v>38</v>
+      </c>
+      <c r="D79">
+        <v>75.2</v>
+      </c>
+      <c r="E79">
+        <v>86.4</v>
+      </c>
+      <c r="F79">
+        <v>14.8</v>
+      </c>
+      <c r="G79" t="s">
+        <v>12</v>
+      </c>
+      <c r="H79" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>62</v>
+      </c>
+      <c r="B80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80">
+        <v>53.8</v>
+      </c>
+      <c r="E80">
+        <v>61.3</v>
+      </c>
+      <c r="F80">
+        <v>13.8</v>
+      </c>
+      <c r="G80" t="s">
+        <v>12</v>
+      </c>
+      <c r="H80" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>62</v>
+      </c>
+      <c r="B81" t="s">
+        <v>45</v>
+      </c>
+      <c r="C81" t="s">
+        <v>46</v>
+      </c>
+      <c r="D81">
+        <v>148.8</v>
+      </c>
+      <c r="E81">
+        <v>168.8</v>
+      </c>
+      <c r="F81">
+        <v>13.4</v>
+      </c>
+      <c r="G81">
+        <v>90.6</v>
+      </c>
+      <c r="H81">
+        <v>86.2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>62</v>
+      </c>
+      <c r="B82" t="s">
+        <v>63</v>
+      </c>
+      <c r="C82" t="s">
+        <v>64</v>
+      </c>
+      <c r="D82">
+        <v>66</v>
+      </c>
+      <c r="E82">
+        <v>74.2</v>
+      </c>
+      <c r="F82">
+        <v>12.5</v>
+      </c>
+      <c r="G82" t="s">
+        <v>12</v>
+      </c>
+      <c r="H82" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B83" t="s">
+        <v>19</v>
+      </c>
+      <c r="C83" t="s">
+        <v>25</v>
+      </c>
+      <c r="D83">
+        <v>98.7</v>
+      </c>
+      <c r="E83">
+        <v>110.6</v>
+      </c>
+      <c r="F83">
+        <v>12</v>
+      </c>
+      <c r="G83">
+        <v>90.6</v>
+      </c>
+      <c r="H83">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>62</v>
+      </c>
+      <c r="B84" t="s">
+        <v>35</v>
+      </c>
+      <c r="C84" t="s">
+        <v>36</v>
+      </c>
+      <c r="D84">
+        <v>82.5</v>
+      </c>
+      <c r="E84">
+        <v>92</v>
+      </c>
+      <c r="F84">
+        <v>11.5</v>
+      </c>
+      <c r="G84">
+        <v>90.6</v>
+      </c>
+      <c r="H84">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>62</v>
+      </c>
+      <c r="B85" t="s">
+        <v>47</v>
+      </c>
+      <c r="C85" t="s">
+        <v>48</v>
+      </c>
+      <c r="D85">
+        <v>97.5</v>
+      </c>
+      <c r="E85">
+        <v>107.9</v>
+      </c>
+      <c r="F85">
+        <v>10.6</v>
+      </c>
+      <c r="G85">
+        <v>90.6</v>
+      </c>
+      <c r="H85">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>62</v>
+      </c>
+      <c r="B86" t="s">
+        <v>60</v>
+      </c>
+      <c r="C86" t="s">
+        <v>61</v>
+      </c>
+      <c r="D86">
+        <v>94</v>
+      </c>
+      <c r="E86">
+        <v>102.9</v>
+      </c>
+      <c r="F86">
+        <v>9.4</v>
+      </c>
+      <c r="G86">
+        <v>90.6</v>
+      </c>
+      <c r="H86">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>62</v>
+      </c>
+      <c r="B87" t="s">
+        <v>49</v>
+      </c>
+      <c r="C87" t="s">
+        <v>50</v>
+      </c>
+      <c r="D87">
+        <v>97.4</v>
+      </c>
+      <c r="E87">
+        <v>105.1</v>
+      </c>
+      <c r="F87">
+        <v>7.8</v>
+      </c>
+      <c r="G87">
+        <v>90.6</v>
+      </c>
+      <c r="H87">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>62</v>
+      </c>
+      <c r="B88" t="s">
+        <v>49</v>
+      </c>
+      <c r="C88" t="s">
+        <v>51</v>
+      </c>
+      <c r="D88">
+        <v>108.2</v>
+      </c>
+      <c r="E88">
+        <v>115.7</v>
+      </c>
+      <c r="F88">
+        <v>6.9</v>
+      </c>
+      <c r="G88">
+        <v>90.6</v>
+      </c>
+      <c r="H88">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>62</v>
+      </c>
+      <c r="B89" t="s">
+        <v>55</v>
+      </c>
+      <c r="C89" t="s">
+        <v>56</v>
+      </c>
+      <c r="D89">
+        <v>98.3</v>
+      </c>
+      <c r="E89">
+        <v>104.5</v>
+      </c>
+      <c r="F89">
+        <v>6.3</v>
+      </c>
+      <c r="G89">
+        <v>90.6</v>
+      </c>
+      <c r="H89">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>62</v>
+      </c>
+      <c r="B90" t="s">
+        <v>27</v>
+      </c>
+      <c r="C90" t="s">
+        <v>28</v>
+      </c>
+      <c r="D90">
+        <v>106.4</v>
+      </c>
+      <c r="E90">
+        <v>111.8</v>
+      </c>
+      <c r="F90">
+        <v>5</v>
+      </c>
+      <c r="G90">
+        <v>90.6</v>
+      </c>
+      <c r="H90">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>62</v>
+      </c>
+      <c r="B91" t="s">
+        <v>43</v>
+      </c>
+      <c r="C91" t="s">
+        <v>44</v>
+      </c>
+      <c r="D91">
+        <v>108.7</v>
+      </c>
+      <c r="E91">
+        <v>113.1</v>
+      </c>
+      <c r="F91">
+        <v>4</v>
+      </c>
+      <c r="G91">
+        <v>90.6</v>
+      </c>
+      <c r="H91">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>62</v>
+      </c>
+      <c r="B92" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" t="s">
+        <v>16</v>
+      </c>
+      <c r="D92">
+        <v>96.3</v>
+      </c>
+      <c r="E92">
+        <v>100.2</v>
+      </c>
+      <c r="F92">
+        <v>4</v>
+      </c>
+      <c r="G92">
+        <v>90.6</v>
+      </c>
+      <c r="H92">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>62</v>
+      </c>
+      <c r="B93" t="s">
+        <v>47</v>
+      </c>
+      <c r="C93" t="s">
+        <v>52</v>
+      </c>
+      <c r="D93">
+        <v>107.6</v>
+      </c>
+      <c r="E93">
+        <v>110.3</v>
+      </c>
+      <c r="F93">
+        <v>2.5</v>
+      </c>
+      <c r="G93">
+        <v>90.6</v>
+      </c>
+      <c r="H93">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>62</v>
+      </c>
+      <c r="B94" t="s">
+        <v>47</v>
+      </c>
+      <c r="C94" t="s">
+        <v>53</v>
+      </c>
+      <c r="D94">
+        <v>112.5</v>
+      </c>
+      <c r="E94">
+        <v>111.7</v>
+      </c>
+      <c r="F94">
+        <v>-0.7</v>
+      </c>
+      <c r="G94">
+        <v>90.6</v>
+      </c>
+      <c r="H94">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>62</v>
+      </c>
+      <c r="B95" t="s">
+        <v>57</v>
+      </c>
+      <c r="C95" t="s">
+        <v>58</v>
+      </c>
+      <c r="D95">
+        <v>108.6</v>
+      </c>
+      <c r="E95">
+        <v>104.6</v>
+      </c>
+      <c r="F95">
+        <v>-3.7</v>
+      </c>
+      <c r="G95">
+        <v>90.6</v>
+      </c>
+      <c r="H95">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>65</v>
+      </c>
+      <c r="B96" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96">
+        <v>40.2</v>
+      </c>
+      <c r="E96">
+        <v>51.1</v>
+      </c>
+      <c r="F96">
+        <v>27.3</v>
+      </c>
+      <c r="G96" t="s">
+        <v>12</v>
+      </c>
+      <c r="H96" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>65</v>
+      </c>
+      <c r="B97" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97">
+        <v>75.2</v>
+      </c>
+      <c r="E97">
+        <v>89.4</v>
+      </c>
+      <c r="F97">
+        <v>18.7</v>
+      </c>
+      <c r="G97" t="s">
+        <v>12</v>
+      </c>
+      <c r="H97" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>65</v>
+      </c>
+      <c r="B98" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98">
+        <v>73.1</v>
+      </c>
+      <c r="E98">
+        <v>86.8</v>
+      </c>
+      <c r="F98">
+        <v>18.7</v>
+      </c>
+      <c r="G98" t="s">
+        <v>12</v>
+      </c>
+      <c r="H98" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>65</v>
+      </c>
+      <c r="B99" t="s">
+        <v>33</v>
+      </c>
+      <c r="C99" t="s">
+        <v>34</v>
+      </c>
+      <c r="D99">
+        <v>61.5</v>
+      </c>
+      <c r="E99">
+        <v>72.9</v>
+      </c>
+      <c r="F99">
+        <v>18.5</v>
+      </c>
+      <c r="G99" t="s">
+        <v>12</v>
+      </c>
+      <c r="H99" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>65</v>
+      </c>
+      <c r="B100" t="s">
+        <v>40</v>
+      </c>
+      <c r="C100" t="s">
+        <v>41</v>
+      </c>
+      <c r="D100">
+        <v>76.6</v>
+      </c>
+      <c r="E100">
+        <v>88.7</v>
+      </c>
+      <c r="F100">
+        <v>15.7</v>
+      </c>
+      <c r="G100" t="s">
+        <v>12</v>
+      </c>
+      <c r="H100" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>65</v>
+      </c>
+      <c r="B101" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" t="s">
+        <v>25</v>
+      </c>
+      <c r="D101">
+        <v>98.7</v>
+      </c>
+      <c r="E101">
+        <v>113.4</v>
+      </c>
+      <c r="F101">
+        <v>14.9</v>
+      </c>
+      <c r="G101">
+        <v>90.4</v>
+      </c>
+      <c r="H101">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>65</v>
+      </c>
+      <c r="B102" t="s">
+        <v>37</v>
+      </c>
+      <c r="C102" t="s">
+        <v>38</v>
+      </c>
+      <c r="D102">
+        <v>75.2</v>
+      </c>
+      <c r="E102">
+        <v>86.1</v>
+      </c>
+      <c r="F102">
+        <v>14.3</v>
+      </c>
+      <c r="G102" t="s">
+        <v>12</v>
+      </c>
+      <c r="H102" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>65</v>
+      </c>
+      <c r="B103" t="s">
+        <v>17</v>
+      </c>
+      <c r="C103" t="s">
+        <v>18</v>
+      </c>
+      <c r="D103">
+        <v>53.8</v>
+      </c>
+      <c r="E103">
+        <v>61.4</v>
+      </c>
+      <c r="F103">
+        <v>14.1</v>
+      </c>
+      <c r="G103" t="s">
+        <v>12</v>
+      </c>
+      <c r="H103" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>65</v>
+      </c>
+      <c r="B104" t="s">
+        <v>45</v>
+      </c>
+      <c r="C104" t="s">
+        <v>46</v>
+      </c>
+      <c r="D104">
+        <v>148.8</v>
+      </c>
+      <c r="E104">
+        <v>168.4</v>
+      </c>
+      <c r="F104">
+        <v>13.1</v>
+      </c>
+      <c r="G104">
+        <v>90.4</v>
+      </c>
+      <c r="H104">
+        <v>86.1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>65</v>
+      </c>
+      <c r="B105" t="s">
+        <v>63</v>
+      </c>
+      <c r="C105" t="s">
+        <v>64</v>
+      </c>
+      <c r="D105">
+        <v>66</v>
+      </c>
+      <c r="E105">
+        <v>74.5</v>
+      </c>
+      <c r="F105">
+        <v>12.9</v>
+      </c>
+      <c r="G105" t="s">
+        <v>12</v>
+      </c>
+      <c r="H105" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>65</v>
+      </c>
+      <c r="B106" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" t="s">
+        <v>26</v>
+      </c>
+      <c r="D106">
+        <v>57.9</v>
+      </c>
+      <c r="E106">
+        <v>65.2</v>
+      </c>
+      <c r="F106">
+        <v>12.6</v>
+      </c>
+      <c r="G106" t="s">
+        <v>12</v>
+      </c>
+      <c r="H106" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>65</v>
+      </c>
+      <c r="B107" t="s">
+        <v>35</v>
+      </c>
+      <c r="C107" t="s">
+        <v>36</v>
+      </c>
+      <c r="D107">
+        <v>82.5</v>
+      </c>
+      <c r="E107">
+        <v>92.1</v>
+      </c>
+      <c r="F107">
+        <v>11.6</v>
+      </c>
+      <c r="G107">
+        <v>90.4</v>
+      </c>
+      <c r="H107">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>65</v>
+      </c>
+      <c r="B108" t="s">
+        <v>47</v>
+      </c>
+      <c r="C108" t="s">
+        <v>48</v>
+      </c>
+      <c r="D108">
+        <v>97.5</v>
+      </c>
+      <c r="E108">
+        <v>108</v>
+      </c>
+      <c r="F108">
+        <v>10.7</v>
+      </c>
+      <c r="G108">
+        <v>90.4</v>
+      </c>
+      <c r="H108">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>65</v>
+      </c>
+      <c r="B109" t="s">
+        <v>60</v>
+      </c>
+      <c r="C109" t="s">
+        <v>61</v>
+      </c>
+      <c r="D109">
+        <v>94</v>
+      </c>
+      <c r="E109">
+        <v>102.8</v>
+      </c>
+      <c r="F109">
+        <v>9.3</v>
+      </c>
+      <c r="G109">
+        <v>90.4</v>
+      </c>
+      <c r="H109">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>65</v>
+      </c>
+      <c r="B110" t="s">
+        <v>66</v>
+      </c>
+      <c r="C110" t="s">
+        <v>67</v>
+      </c>
+      <c r="D110">
+        <v>91.7</v>
+      </c>
+      <c r="E110">
+        <v>100.1</v>
+      </c>
+      <c r="F110">
+        <v>9.1</v>
+      </c>
+      <c r="G110">
+        <v>90.4</v>
+      </c>
+      <c r="H110">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>65</v>
+      </c>
+      <c r="B111" t="s">
+        <v>49</v>
+      </c>
+      <c r="C111" t="s">
+        <v>50</v>
+      </c>
+      <c r="D111">
+        <v>97.4</v>
+      </c>
+      <c r="E111">
+        <v>105.2</v>
+      </c>
+      <c r="F111">
+        <v>8</v>
+      </c>
+      <c r="G111">
+        <v>90.4</v>
+      </c>
+      <c r="H111">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>65</v>
+      </c>
+      <c r="B112" t="s">
+        <v>49</v>
+      </c>
+      <c r="C112" t="s">
+        <v>51</v>
+      </c>
+      <c r="D112">
+        <v>108.2</v>
+      </c>
+      <c r="E112">
+        <v>115.7</v>
+      </c>
+      <c r="F112">
+        <v>6.9</v>
+      </c>
+      <c r="G112">
+        <v>90.4</v>
+      </c>
+      <c r="H112">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>65</v>
+      </c>
+      <c r="B113" t="s">
+        <v>55</v>
+      </c>
+      <c r="C113" t="s">
+        <v>56</v>
+      </c>
+      <c r="D113">
+        <v>98.3</v>
+      </c>
+      <c r="E113">
+        <v>104.7</v>
+      </c>
+      <c r="F113">
+        <v>6.5</v>
+      </c>
+      <c r="G113">
+        <v>90.4</v>
+      </c>
+      <c r="H113">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>65</v>
+      </c>
+      <c r="B114" t="s">
+        <v>43</v>
+      </c>
+      <c r="C114" t="s">
+        <v>44</v>
+      </c>
+      <c r="D114">
+        <v>108.7</v>
+      </c>
+      <c r="E114">
+        <v>113.2</v>
+      </c>
+      <c r="F114">
+        <v>4.1</v>
+      </c>
+      <c r="G114">
+        <v>90.4</v>
+      </c>
+      <c r="H114">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>65</v>
+      </c>
+      <c r="B115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C115" t="s">
+        <v>28</v>
+      </c>
+      <c r="D115">
+        <v>106.4</v>
+      </c>
+      <c r="E115">
+        <v>110</v>
+      </c>
+      <c r="F115">
+        <v>3.3</v>
+      </c>
+      <c r="G115">
+        <v>90.4</v>
+      </c>
+      <c r="H115">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>65</v>
+      </c>
+      <c r="B116" t="s">
+        <v>47</v>
+      </c>
+      <c r="C116" t="s">
+        <v>52</v>
+      </c>
+      <c r="D116">
+        <v>107.6</v>
+      </c>
+      <c r="E116">
+        <v>110.9</v>
+      </c>
+      <c r="F116">
+        <v>2.9</v>
+      </c>
+      <c r="G116">
+        <v>90.4</v>
+      </c>
+      <c r="H116">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>65</v>
+      </c>
+      <c r="B117" t="s">
+        <v>47</v>
+      </c>
+      <c r="C117" t="s">
+        <v>53</v>
+      </c>
+      <c r="D117">
+        <v>112.5</v>
+      </c>
+      <c r="E117">
+        <v>110.6</v>
+      </c>
+      <c r="F117">
+        <v>-1.6</v>
+      </c>
+      <c r="G117">
+        <v>90.4</v>
+      </c>
+      <c r="H117">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>65</v>
+      </c>
+      <c r="B118" t="s">
+        <v>57</v>
+      </c>
+      <c r="C118" t="s">
+        <v>58</v>
+      </c>
+      <c r="D118">
+        <v>108.6</v>
+      </c>
+      <c r="E118">
+        <v>104.6</v>
+      </c>
+      <c r="F118">
+        <v>-3.7</v>
+      </c>
+      <c r="G118">
+        <v>90.4</v>
+      </c>
+      <c r="H118">
+        <v>15.6</v>
       </c>
     </row>
   </sheetData>

--- a/source/8、绩效异常岗位/4、供件岗/供件岗-6月.xlsx
+++ b/source/8、绩效异常岗位/4、供件岗/供件岗-6月.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I419"/>
+  <dimension ref="A1:I542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16481,6 +16481,4725 @@
         <v>11.2</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="F420" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="G420" t="n">
+        <v>27</v>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="F421" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="G421" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="F422" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="G422" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>甘肃区</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="F423" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="G423" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>肃宁</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F424" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="G424" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>辽宁区</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="F425" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="G425" t="n">
+        <v>14</v>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>广西区</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>柳州</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="F426" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G426" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F427" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="G427" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="F428" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="G428" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H428" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I428" t="n">
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F429" t="n">
+        <v>104</v>
+      </c>
+      <c r="G429" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H429" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I429" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>100</v>
+      </c>
+      <c r="F430" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="G430" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H430" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I430" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="F431" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="G431" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H431" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I431" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="F432" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="G432" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H432" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I432" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="F433" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="G433" t="n">
+        <v>4</v>
+      </c>
+      <c r="H433" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I433" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="F434" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="G434" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H434" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I434" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>芜湖</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F435" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="G435" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H435" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I435" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F436" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="G436" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H436" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I436" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F437" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="G437" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="H437" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I437" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="F438" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G438" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="H438" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I438" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="F439" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="G439" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="H439" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I439" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>云南区</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="F440" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="G440" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="H440" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I440" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="F441" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="G441" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="F442" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="G442" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>甘肃区</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="F443" t="n">
+        <v>76</v>
+      </c>
+      <c r="G443" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>肃宁</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F444" t="n">
+        <v>86</v>
+      </c>
+      <c r="G444" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>辽宁区</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="F445" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="G445" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>广西区</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>柳州</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="F446" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="G446" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="F447" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="G447" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H447" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I447" t="n">
+        <v>85.5</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F448" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="G448" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H448" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I448" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F449" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="G449" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>100</v>
+      </c>
+      <c r="F450" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="G450" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H450" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I450" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="F451" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="G451" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H451" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I451" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="F452" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="G452" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H452" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I452" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F453" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="G453" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H453" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I453" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="F454" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="G454" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H454" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I454" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="F455" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="G455" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H455" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I455" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>芜湖</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F456" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G456" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H456" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I456" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F457" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="G457" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="H457" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I457" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F458" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="G458" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H458" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I458" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="F459" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="G459" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="H459" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I459" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="F460" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="G460" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="H460" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I460" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>云南区</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="F461" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="G461" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="H461" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I461" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="F462" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="G462" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="F463" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="G463" t="n">
+        <v>16</v>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>甘肃区</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="F464" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="G464" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>肃宁</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F465" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="G465" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>辽宁区</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="F466" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="G466" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>广西区</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>柳州</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="F467" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="G467" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F468" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="G468" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H468" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I468" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="F469" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="G469" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H469" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I469" t="n">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>100</v>
+      </c>
+      <c r="F470" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="G470" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H470" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I470" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="F471" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="G471" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H471" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I471" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="F472" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="G472" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H472" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I472" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F473" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="G473" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H473" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I473" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="F474" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="G474" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H474" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I474" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>芜湖</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F475" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="G475" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H475" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I475" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="F476" t="n">
+        <v>114</v>
+      </c>
+      <c r="G476" t="n">
+        <v>3</v>
+      </c>
+      <c r="H476" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I476" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F477" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="G477" t="n">
+        <v>0</v>
+      </c>
+      <c r="H477" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I477" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F478" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="G478" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="H478" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I478" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="F479" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G479" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="H479" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I479" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="F480" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="G480" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H480" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I480" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>云南区</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="F481" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="G481" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="H481" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I481" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="F482" t="n">
+        <v>70</v>
+      </c>
+      <c r="G482" t="n">
+        <v>24</v>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="F483" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="G483" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>甘肃区</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="F484" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="G484" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>肃宁</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F485" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="G485" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>辽宁区</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="F486" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="G486" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>广西区</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>柳州</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="F487" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G487" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F488" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="G488" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="F489" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="G489" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H489" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I489" t="n">
+        <v>85.40000000000001</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F490" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="G490" t="n">
+        <v>11</v>
+      </c>
+      <c r="H490" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I490" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>100</v>
+      </c>
+      <c r="F491" t="n">
+        <v>107</v>
+      </c>
+      <c r="G491" t="n">
+        <v>7</v>
+      </c>
+      <c r="H491" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I491" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="F492" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="G492" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H492" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I492" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="F493" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="G493" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H493" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I493" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F494" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="G494" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H494" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I494" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="F495" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="G495" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H495" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I495" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="F496" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="G496" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H496" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I496" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>芜湖</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F497" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="G497" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H497" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I497" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F498" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="G498" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H498" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I498" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F499" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="G499" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H499" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I499" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="F500" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G500" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="H500" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I500" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="F501" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="G501" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="H501" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I501" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>云南区</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="F502" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="G502" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H502" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I502" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="F503" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="G503" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>甘肃区</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="F504" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="G504" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="F505" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="G505" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>肃宁</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F506" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="G506" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>辽宁区</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="F507" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="G507" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="F508" t="n">
+        <v>106</v>
+      </c>
+      <c r="G508" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H508" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I508" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>广西区</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>柳州</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="F509" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="G509" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="F510" t="n">
+        <v>164.3</v>
+      </c>
+      <c r="G510" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H510" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I510" t="n">
+        <v>85.5</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F511" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="G511" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>100</v>
+      </c>
+      <c r="F512" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="G512" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H512" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I512" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="F513" t="n">
+        <v>112</v>
+      </c>
+      <c r="G513" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H513" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I513" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F514" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="G514" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H514" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I514" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="F515" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="G515" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H515" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I515" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="F516" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="G516" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H516" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I516" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>芜湖</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F517" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G517" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H517" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I517" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F518" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="G518" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="H518" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I518" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F519" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="G519" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H519" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I519" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="F520" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="G520" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H520" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I520" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="F521" t="n">
+        <v>110</v>
+      </c>
+      <c r="G521" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="H521" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I521" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>云南区</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="F522" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="G522" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="H522" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I522" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F523" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="G523" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>甘肃区</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="F524" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="G524" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="F525" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="G525" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>肃宁</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F526" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="G526" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="F527" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="G527" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H527" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I527" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>辽宁区</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="F528" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="G528" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>广西区</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>柳州</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="F529" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="G529" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F530" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="G530" t="n">
+        <v>11</v>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="F531" t="n">
+        <v>164.2</v>
+      </c>
+      <c r="G531" t="n">
+        <v>11</v>
+      </c>
+      <c r="H531" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I531" t="n">
+        <v>85.40000000000001</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>100</v>
+      </c>
+      <c r="F532" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="G532" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H532" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I532" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="F533" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="G533" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H533" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I533" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F534" t="n">
+        <v>98</v>
+      </c>
+      <c r="G534" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H534" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I534" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="F535" t="n">
+        <v>110</v>
+      </c>
+      <c r="G535" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H535" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I535" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="F536" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="G536" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H536" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I536" t="n">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>芜湖</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F537" t="n">
+        <v>100</v>
+      </c>
+      <c r="G537" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H537" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I537" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F538" t="n">
+        <v>107</v>
+      </c>
+      <c r="G538" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="H538" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I538" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F539" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="G539" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="H539" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I539" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="F540" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="G540" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H540" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I540" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="F541" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="G541" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="H541" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I541" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>供件岗</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>云南区</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="F542" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="G542" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="H542" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I542" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
